--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486430_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486430_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2242</v>
+        <v>7.5144</v>
       </c>
       <c r="E2" t="n">
-        <v>8.765000000000001</v>
+        <v>8.7469</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.5408</v>
+        <v>-1.2326</v>
       </c>
       <c r="G2" t="n">
         <v>8.497199999999999</v>
@@ -610,13 +610,13 @@
         <v>3.2626</v>
       </c>
       <c r="S2" t="n">
-        <v>0.024</v>
+        <v>0.3142</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0587</v>
+        <v>1.0407</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.0347</v>
+        <v>-0.7264</v>
       </c>
       <c r="V2" t="n">
         <v>-3.4721</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. SMITH</t>
+          <t>S. NIANG BEYE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.335</v>
+        <v>2.8252</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9868</v>
+        <v>2.1246</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3482</v>
+        <v>0.7006</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4353</v>
+        <v>-0.5302</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9947</v>
+        <v>-0.1796</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5594</v>
+        <v>-0.3506</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9605</v>
+        <v>1.1585</v>
       </c>
       <c r="K3" t="n">
-        <v>0.119</v>
+        <v>-0.5078</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8415</v>
+        <v>1.6663</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5252</v>
+        <v>-1.6887</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8757</v>
+        <v>0.3282</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.4009</v>
+        <v>-2.0169</v>
       </c>
       <c r="P3" t="n">
-        <v>0.435</v>
+        <v>3.4801</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.6101</v>
+        <v>3.4801</v>
       </c>
       <c r="S3" t="n">
-        <v>2.7729</v>
+        <v>1.0875</v>
       </c>
       <c r="T3" t="n">
-        <v>3.2013</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4284</v>
+        <v>0.1214</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3082</v>
+        <v>-1.2122</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3082</v>
+        <v>-1.2122</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. NIANG BEYE</t>
+          <t>A. SCARIOLO ARES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5563</v>
+        <v>1.4159</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6091</v>
+        <v>1.473</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9472</v>
+        <v>-0.0571</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5302</v>
+        <v>1.3515</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1796</v>
+        <v>2.0742</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3506</v>
+        <v>-0.7228</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1585</v>
+        <v>3.3868</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.5078</v>
+        <v>1.6456</v>
       </c>
       <c r="L4" t="n">
-        <v>1.6663</v>
+        <v>1.7412</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.6887</v>
+        <v>-2.0353</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3282</v>
+        <v>0.4286</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.0169</v>
+        <v>-2.4639</v>
       </c>
       <c r="P4" t="n">
-        <v>3.4801</v>
+        <v>0.6525</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R4" t="n">
-        <v>3.4801</v>
+        <v>2.8276</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8186</v>
+        <v>-0.3314</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4506</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3679</v>
+        <v>-0.3975</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.2122</v>
+        <v>-0.2568</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2122</v>
+        <v>-0.452</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. ARAMBURU LAMY</t>
+          <t>L. SMITH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4802</v>
+        <v>1.3495</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7819</v>
+        <v>0.1554</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2621</v>
+        <v>1.1941</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7456</v>
+        <v>0.4353</v>
       </c>
       <c r="H5" t="n">
-        <v>2.3904</v>
+        <v>0.9947</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.6447</v>
+        <v>-0.5594</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8398</v>
+        <v>0.9605</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0622</v>
+        <v>0.119</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.2224</v>
+        <v>0.8415</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.09420000000000001</v>
+        <v>-0.5252</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3282</v>
+        <v>0.8757</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4224</v>
+        <v>-1.4009</v>
       </c>
       <c r="P5" t="n">
-        <v>1.305</v>
+        <v>0.435</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3926</v>
+        <v>2.6101</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0055</v>
+        <v>0.7874</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7294</v>
+        <v>1.3699</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.276</v>
+        <v>-0.5825</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.3082</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.7602</v>
+        <v>-0.3082</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. SCARIOLO ARES</t>
+          <t>J. ARAMBURU LAMY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4611</v>
+        <v>0.8052</v>
       </c>
       <c r="E6" t="n">
-        <v>0.734</v>
+        <v>-0.2412</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2729</v>
+        <v>1.0464</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3515</v>
+        <v>0.7456</v>
       </c>
       <c r="H6" t="n">
-        <v>2.0742</v>
+        <v>2.3904</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7228</v>
+        <v>-1.6447</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3868</v>
+        <v>0.8398</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6456</v>
+        <v>2.0622</v>
       </c>
       <c r="L6" t="n">
-        <v>1.7412</v>
+        <v>-1.2224</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0353</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4286</v>
+        <v>0.3282</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.4639</v>
+        <v>-0.4224</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R6" t="n">
-        <v>2.8276</v>
+        <v>2.3926</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2862</v>
+        <v>-0.6805</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.1887</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6132</v>
+        <v>-0.4918</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2568</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W6" t="n">
         <v>0.1952</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.452</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.204</v>
+        <v>0.3685</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5855</v>
+        <v>0.1103</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3815</v>
+        <v>0.2582</v>
       </c>
       <c r="G7" t="n">
         <v>2.1458</v>
@@ -1000,13 +1000,13 @@
         <v>1.7401</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7143</v>
+        <v>-0.1418</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3749</v>
+        <v>0.3209</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3394</v>
+        <v>-0.4627</v>
       </c>
       <c r="V7" t="n">
         <v>-0.113</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.211</v>
+        <v>-1.6214</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8789</v>
+        <v>-1.3201</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.332</v>
+        <v>-0.3012</v>
       </c>
       <c r="G8" t="n">
         <v>-2.4953</v>
@@ -1078,13 +1078,13 @@
         <v>1.7401</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1475</v>
+        <v>-0.5579</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3869</v>
+        <v>0.1719</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7606000000000001</v>
+        <v>-0.7297</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3082</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2986</v>
+        <v>-2.3534</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.083</v>
+        <v>-1.0145</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2156</v>
+        <v>-1.3389</v>
       </c>
       <c r="G9" t="n">
         <v>-1.622</v>
@@ -1156,13 +1156,13 @@
         <v>0.2175</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6782</v>
+        <v>-0.733</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.411</v>
+        <v>-0.3425</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2673</v>
+        <v>-0.3906</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2159</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8212</v>
+        <v>-2.8106</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0614</v>
+        <v>-3.3282</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2402</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="G10" t="n">
         <v>-2.1716</v>
@@ -1234,13 +1234,13 @@
         <v>1.9576</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.649</v>
+        <v>-0.6384</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0036</v>
+        <v>-0.2632</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6526</v>
+        <v>-0.3752</v>
       </c>
       <c r="V10" t="n">
         <v>1.3045</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.907</v>
+        <v>-4.851</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.4905</v>
+        <v>-5.4653</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5835</v>
+        <v>0.6143</v>
       </c>
       <c r="G11" t="n">
         <v>-2.4393</v>
@@ -1312,13 +1312,13 @@
         <v>1.5225</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0326</v>
+        <v>0.0886</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4146</v>
+        <v>0.4398</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.382</v>
+        <v>-0.3512</v>
       </c>
       <c r="V11" t="n">
         <v>-0.7602</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.615000000000001</v>
+        <v>2.642300000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2137000000000011</v>
+        <v>1.2409</v>
       </c>
       <c r="F12" t="n">
         <v>1.4014</v>
@@ -1372,7 +1372,7 @@
         <v>9.215999999999998</v>
       </c>
       <c r="M12" t="n">
-        <v>-8.145000000000001</v>
+        <v>-8.145</v>
       </c>
       <c r="N12" t="n">
         <v>3.2064</v>
@@ -1390,13 +1390,13 @@
         <v>21.7508</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.8326</v>
+        <v>-0.8053</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5537</v>
+        <v>3.5811</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.386299999999999</v>
+        <v>-4.386200000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-5.9071</v>
@@ -1405,7 +1405,7 @@
         <v>1.9109</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.818</v>
+        <v>-7.818000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.682</v>
+        <v>4.0288</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5236</v>
+        <v>2.7472</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1583</v>
+        <v>1.2816</v>
       </c>
       <c r="G13" t="n">
         <v>2.6803</v>
@@ -1468,13 +1468,13 @@
         <v>0.6525</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2158</v>
+        <v>0.131</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.411</v>
+        <v>-0.1875</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1952</v>
+        <v>0.3184</v>
       </c>
       <c r="V13" t="n">
         <v>0.5649999999999999</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. BELEMENE-DZABATOU</t>
+          <t>J. KASIBABU SHILALA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6918</v>
+        <v>2.7075</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6039</v>
+        <v>0.8935999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0879</v>
+        <v>1.8139</v>
       </c>
       <c r="G14" t="n">
-        <v>1.6501</v>
+        <v>0.4277</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3314</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3188</v>
+        <v>1.0088</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3793</v>
+        <v>1.6878</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3832</v>
+        <v>0.0032</v>
       </c>
       <c r="L14" t="n">
-        <v>0.9961</v>
+        <v>1.6846</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2708</v>
+        <v>-1.2601</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0519</v>
+        <v>-0.5843</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3227</v>
+        <v>-0.6758</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2175</v>
+        <v>-2.3926</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.7401</v>
+        <v>-4.7852</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9576</v>
+        <v>2.3926</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1732</v>
+        <v>1.2618</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1837</v>
+        <v>0.5804</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0105</v>
+        <v>0.6813</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3491</v>
+        <v>3.4106</v>
       </c>
       <c r="W14" t="n">
-        <v>0.7809</v>
+        <v>3.4106</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. KASIBABU SHILALA</t>
+          <t>J. BELEMENE-DZABATOU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5931</v>
+        <v>2.598</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5584</v>
+        <v>1.2686</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0347</v>
+        <v>1.3294</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4277</v>
+        <v>1.6501</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5810999999999999</v>
+        <v>0.3314</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0088</v>
+        <v>1.3188</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6878</v>
+        <v>1.3793</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0032</v>
+        <v>0.3832</v>
       </c>
       <c r="L15" t="n">
-        <v>1.6846</v>
+        <v>0.9961</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2601</v>
+        <v>0.2708</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5843</v>
+        <v>-0.0519</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6758</v>
+        <v>0.3227</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.3926</v>
+        <v>0.2175</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.7852</v>
+        <v>-1.7401</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3926</v>
+        <v>1.9576</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1474</v>
+        <v>1.0794</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2452</v>
+        <v>0.8484</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9022</v>
+        <v>0.231</v>
       </c>
       <c r="V15" t="n">
-        <v>3.4106</v>
+        <v>-0.3491</v>
       </c>
       <c r="W15" t="n">
-        <v>3.4106</v>
+        <v>0.7809</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. AURRECOECHEA ALCOLADO</t>
+          <t>D. MANCHON CRESPO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.187</v>
+        <v>1.7193</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6878</v>
+        <v>1.8982</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5007</v>
+        <v>-0.1788</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2804</v>
+        <v>-0.11</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3834</v>
+        <v>0.067</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6637999999999999</v>
+        <v>-0.1769</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8761</v>
+        <v>2.3311</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0346</v>
+        <v>0.6847</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8415</v>
+        <v>1.6463</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.1565</v>
+        <v>-2.441</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6512</v>
+        <v>-0.6178</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.5053</v>
+        <v>-1.8233</v>
       </c>
       <c r="P16" t="n">
-        <v>-3.0451</v>
+        <v>1.5225</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.7852</v>
+        <v>-0.6525</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7401</v>
+        <v>2.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>2.9921</v>
+        <v>0.4813</v>
       </c>
       <c r="T16" t="n">
-        <v>3.0764</v>
+        <v>0.3942</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0843</v>
+        <v>0.0871</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5204</v>
+        <v>-0.1745</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5204</v>
+        <v>-0.1745</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.5225</v>
       </c>
       <c r="E17" t="n">
-        <v>2.609</v>
+        <v>3.056</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.919</v>
+        <v>-1.5336</v>
       </c>
       <c r="G17" t="n">
         <v>1.2587</v>
@@ -1780,13 +1780,13 @@
         <v>0.87</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2212</v>
+        <v>-0.3887</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2499</v>
+        <v>0.1971</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9712</v>
+        <v>-0.5858</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. MANCHON CRESPO</t>
+          <t>I. AURRECOECHEA ALCOLADO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1933</v>
+        <v>-0.5677</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0041</v>
+        <v>-0.3239</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8108</v>
+        <v>-0.2438</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.11</v>
+        <v>-0.2804</v>
       </c>
       <c r="H19" t="n">
-        <v>0.067</v>
+        <v>0.3834</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1769</v>
+        <v>-0.6637999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>2.3311</v>
+        <v>1.8761</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6847</v>
+        <v>1.0346</v>
       </c>
       <c r="L19" t="n">
-        <v>1.6463</v>
+        <v>0.8415</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.441</v>
+        <v>-2.1565</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6178</v>
+        <v>-0.6512</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.8233</v>
+        <v>-1.5053</v>
       </c>
       <c r="P19" t="n">
-        <v>1.5225</v>
+        <v>-3.0451</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.6525</v>
+        <v>-4.7852</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1751</v>
+        <v>1.7401</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0448</v>
+        <v>1.2374</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4999</v>
+        <v>1.0647</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5449000000000001</v>
+        <v>0.1727</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1745</v>
+        <v>1.5204</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.1745</v>
+        <v>1.5204</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9399</v>
+        <v>-1.4749</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.5361</v>
+        <v>-3.3126</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5962</v>
+        <v>1.8377</v>
       </c>
       <c r="G20" t="n">
         <v>-1.056</v>
@@ -2014,13 +2014,13 @@
         <v>2.8276</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2912</v>
+        <v>0.7562</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3016</v>
+        <v>0.5252</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0105</v>
+        <v>0.231</v>
       </c>
       <c r="V20" t="n">
         <v>0.5649999999999999</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.087</v>
+        <v>-4.0138</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.1256</v>
+        <v>-4.6843</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0385</v>
+        <v>0.6705</v>
       </c>
       <c r="G21" t="n">
         <v>-4.8076</v>
@@ -2092,13 +2092,13 @@
         <v>1.305</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3084</v>
+        <v>0.3815</v>
       </c>
       <c r="T21" t="n">
-        <v>1.2402</v>
+        <v>0.6814</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9318</v>
+        <v>-0.2998</v>
       </c>
       <c r="V21" t="n">
         <v>1.4997</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.8427</v>
+        <v>-5.3719</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7265</v>
+        <v>-2.9442</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.1162</v>
+        <v>-2.4277</v>
       </c>
       <c r="G22" t="n">
         <v>-3.6798</v>
@@ -2170,13 +2170,13 @@
         <v>2.1751</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5979</v>
+        <v>-0.1271</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4999</v>
+        <v>0.2824</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.098</v>
+        <v>-0.4095</v>
       </c>
       <c r="V22" t="n">
         <v>-1.13</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.6149</v>
+        <v>1.3653</v>
       </c>
       <c r="E23" t="n">
         <v>-1.4014</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2136000000000005</v>
+        <v>2.7667</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.917</v>
+        <v>-3.917000000000001</v>
       </c>
       <c r="H23" t="n">
         <v>-6.0523</v>
@@ -2236,25 +2236,25 @@
         <v>-2.8461</v>
       </c>
       <c r="O23" t="n">
-        <v>-9.2159</v>
+        <v>-9.215900000000001</v>
       </c>
       <c r="P23" t="n">
         <v>-5.437799999999998</v>
       </c>
       <c r="Q23" t="n">
-        <v>-21.7508</v>
+        <v>-21.75079999999999</v>
       </c>
       <c r="R23" t="n">
         <v>16.3131</v>
       </c>
       <c r="S23" t="n">
-        <v>1.832599999999999</v>
+        <v>4.812799999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>4.3864</v>
+        <v>4.3863</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.5538</v>
+        <v>0.4264000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>5.9071</v>
